--- a/MIS Project.xlsx
+++ b/MIS Project.xlsx
@@ -1612,7 +1612,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1668,11 +1668,21 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1681,6 +1691,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1692,38 +1711,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="14">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1741,16 +1737,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7076,15 +7062,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>558745</xdr:colOff>
+          <xdr:colOff>556260</xdr:colOff>
           <xdr:row>0</xdr:row>
-          <xdr:rowOff>36722</xdr:rowOff>
+          <xdr:rowOff>38100</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>7</xdr:col>
-          <xdr:colOff>266240</xdr:colOff>
+          <xdr:colOff>266700</xdr:colOff>
           <xdr:row>3</xdr:row>
-          <xdr:rowOff>167955</xdr:rowOff>
+          <xdr:rowOff>167640</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -14065,6 +14051,1301 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C949198-8F70-441F-A8E1-9A552C3157DE}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="E9:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="37">
+        <item x="1"/>
+        <item x="34"/>
+        <item x="15"/>
+        <item x="29"/>
+        <item x="4"/>
+        <item x="35"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="31"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="32"/>
+        <item x="27"/>
+        <item x="19"/>
+        <item x="33"/>
+        <item x="22"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="3" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E8826C3-3CF3-4235-BDB6-24F83A288A4D}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
+  <location ref="B19:C28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="37">
+        <item x="1"/>
+        <item x="34"/>
+        <item x="15"/>
+        <item x="29"/>
+        <item x="4"/>
+        <item x="35"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="31"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="32"/>
+        <item x="27"/>
+        <item x="19"/>
+        <item x="33"/>
+        <item x="22"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C263A915-9F53-406C-BEF9-F9DCB84E4559}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="29">
+  <location ref="H25:I28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="37">
+        <item x="1"/>
+        <item x="34"/>
+        <item x="15"/>
+        <item x="29"/>
+        <item x="4"/>
+        <item x="35"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="31"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="32"/>
+        <item x="27"/>
+        <item x="19"/>
+        <item x="33"/>
+        <item x="22"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="9" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="18" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="22" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="22" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="22" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="27" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0278DCDE-9AA2-4B3C-B354-B5115B4541FB}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="E13:F15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" measureFilter="1">
+      <items count="12">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" measureFilter="1">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="37">
+        <item x="1"/>
+        <item x="34"/>
+        <item x="15"/>
+        <item x="29"/>
+        <item x="4"/>
+        <item x="35"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="31"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="32"/>
+        <item x="27"/>
+        <item x="19"/>
+        <item x="33"/>
+        <item x="22"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="2">
+    <filter fld="3" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+    <filter fld="2" type="count" evalOrder="-1" id="2" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA31B8B-421B-4965-AC6B-B4A21803E69F}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="E25:F28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="37">
+        <item x="1"/>
+        <item x="34"/>
+        <item x="15"/>
+        <item x="29"/>
+        <item x="4"/>
+        <item x="35"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="31"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="32"/>
+        <item x="27"/>
+        <item x="19"/>
+        <item x="33"/>
+        <item x="22"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="9" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="22" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="22" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="22" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{60023E23-E901-4232-A689-EF201C80A91A}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="K9:L16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="12">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="37">
+        <item x="1"/>
+        <item x="34"/>
+        <item x="15"/>
+        <item x="29"/>
+        <item x="4"/>
+        <item x="35"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="31"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="32"/>
+        <item x="27"/>
+        <item x="19"/>
+        <item x="33"/>
+        <item x="22"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="9" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF50603C-7B3E-4851-8D8A-7EFBEE1B4D8A}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
+  <location ref="H9:I16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0" measureFilter="1">
+      <items count="12">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="10"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" measureFilter="1">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="5"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="37">
+        <item x="1"/>
+        <item x="34"/>
+        <item x="15"/>
+        <item x="29"/>
+        <item x="4"/>
+        <item x="35"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="31"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="20"/>
+        <item x="7"/>
+        <item x="30"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="28"/>
+        <item x="24"/>
+        <item x="10"/>
+        <item x="26"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="25"/>
+        <item x="32"/>
+        <item x="27"/>
+        <item x="19"/>
+        <item x="33"/>
+        <item x="22"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="6"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="2">
+    <filter fld="3" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+    <filter fld="2" type="count" evalOrder="-1" id="2" iMeasureFld="0">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{915A8E06-843D-42A0-8C8A-1B4D8C39E64F}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A3:C15" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -14312,1301 +15593,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C949198-8F70-441F-A8E1-9A552C3157DE}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="E9:F11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="8"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="37">
-        <item x="1"/>
-        <item x="34"/>
-        <item x="15"/>
-        <item x="29"/>
-        <item x="4"/>
-        <item x="35"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="31"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="20"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="10"/>
-        <item x="26"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="32"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="33"/>
-        <item x="22"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Profit" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="3" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="1" filterVal="1"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C263A915-9F53-406C-BEF9-F9DCB84E4559}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="29">
-  <location ref="H25:I28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="8"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="37">
-        <item x="1"/>
-        <item x="34"/>
-        <item x="15"/>
-        <item x="29"/>
-        <item x="4"/>
-        <item x="35"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="31"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="20"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="10"/>
-        <item x="26"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="32"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="33"/>
-        <item x="22"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="9" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <chartFormats count="7">
-    <chartFormat chart="18" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="22" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="22" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="22" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="27" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA31B8B-421B-4965-AC6B-B4A21803E69F}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="E25:F28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="8"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="37">
-        <item x="1"/>
-        <item x="34"/>
-        <item x="15"/>
-        <item x="29"/>
-        <item x="4"/>
-        <item x="35"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="31"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="20"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="10"/>
-        <item x="26"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="32"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="33"/>
-        <item x="22"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="9" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="22" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="22" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="22" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{60023E23-E901-4232-A689-EF201C80A91A}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="K9:L16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="8"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="37">
-        <item x="1"/>
-        <item x="34"/>
-        <item x="15"/>
-        <item x="29"/>
-        <item x="4"/>
-        <item x="35"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="31"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="20"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="10"/>
-        <item x="26"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="32"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="33"/>
-        <item x="22"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="9" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF50603C-7B3E-4851-8D8A-7EFBEE1B4D8A}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="H9:I16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0" measureFilter="1">
-      <items count="12">
-        <item x="8"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0" measureFilter="1">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="37">
-        <item x="1"/>
-        <item x="34"/>
-        <item x="15"/>
-        <item x="29"/>
-        <item x="4"/>
-        <item x="35"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="31"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="20"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="10"/>
-        <item x="26"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="32"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="33"/>
-        <item x="22"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Profit" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="2">
-    <filter fld="3" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="1" filterVal="1"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-    <filter fld="2" type="count" evalOrder="-1" id="2" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="1" filterVal="1"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2E8826C3-3CF3-4235-BDB6-24F83A288A4D}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
-  <location ref="B19:C28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="12">
-        <item x="8"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="37">
-        <item x="1"/>
-        <item x="34"/>
-        <item x="15"/>
-        <item x="29"/>
-        <item x="4"/>
-        <item x="35"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="31"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="20"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="10"/>
-        <item x="26"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="32"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="33"/>
-        <item x="22"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Profit" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <chartFormats count="6">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0278DCDE-9AA2-4B3C-B354-B5115B4541FB}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
-  <location ref="E13:F15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" measureFilter="1">
-      <items count="12">
-        <item x="8"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="10"/>
-        <item x="3"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0" measureFilter="1">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="5"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="37">
-        <item x="1"/>
-        <item x="34"/>
-        <item x="15"/>
-        <item x="29"/>
-        <item x="4"/>
-        <item x="35"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="31"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="20"/>
-        <item x="7"/>
-        <item x="30"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="28"/>
-        <item x="24"/>
-        <item x="10"/>
-        <item x="26"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="23"/>
-        <item x="25"/>
-        <item x="32"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="33"/>
-        <item x="22"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="6"/>
-        <item x="14"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Profit" fld="10" baseField="0" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="2">
-    <filter fld="3" type="count" evalOrder="-1" id="1" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="1" filterVal="1"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-    <filter fld="2" type="count" evalOrder="-1" id="2" iMeasureFld="0">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="1" filterVal="1"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Month" xr10:uid="{18CE1468-4B3E-4446-B6C7-2EA2E126C1FF}" sourceName="Month">
   <pivotTables>
@@ -15698,28 +15684,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FCB0E5F3-7A94-4235-9878-6CE82AF8E347}" name="Table1" displayName="Table1" ref="A1:N301" totalsRowShown="0" headerRowDxfId="14" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FCB0E5F3-7A94-4235-9878-6CE82AF8E347}" name="Table1" displayName="Table1" ref="A1:N301" totalsRowShown="0" headerRowDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A1:N301" xr:uid="{FCB0E5F3-7A94-4235-9878-6CE82AF8E347}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N301">
     <sortCondition ref="B1:B301"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{FB2FD81E-BBB8-4599-947C-6D32B15258E8}" name="Transaction ID"/>
-    <tableColumn id="2" xr3:uid="{D7AC9326-559C-4646-9FAD-178DE3CF3630}" name="Date" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{D7AC9326-559C-4646-9FAD-178DE3CF3630}" name="Date" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{5F98717C-1B22-45DF-BFA8-66F901575CC2}" name="Customer name"/>
     <tableColumn id="4" xr3:uid="{F3EB962D-B1A4-40BF-AF2F-BFB5F4CB0129}" name="Product"/>
-    <tableColumn id="10" xr3:uid="{3F67AF38-776B-49B2-A759-B84D23756ABB}" name="Payment Method" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{3F67AF38-776B-49B2-A759-B84D23756ABB}" name="Payment Method" dataDxfId="10"/>
     <tableColumn id="5" xr3:uid="{CF61A7B2-0666-43A3-B964-37CE9C7D7CEA}" name="Unit Sold"/>
-    <tableColumn id="6" xr3:uid="{69AC9F7A-5398-410B-84D7-6E4E83EE57E8}" name="Buying Price" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{7A69A202-D8EA-41A6-95D3-0015094D703C}" name="Selling Price" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{9741974B-D6ED-460F-9C8D-702EA0D3DA7D}" name="Total Buying" dataDxfId="8" dataCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{985209AE-C175-4412-A5E0-92E6C0F7A6EF}" name="Total Sales" dataDxfId="7" dataCellStyle="Currency"/>
-    <tableColumn id="11" xr3:uid="{D7D84B77-8B5F-41B1-AB70-CCD67DBF458A}" name="Profit" dataDxfId="6">
+    <tableColumn id="6" xr3:uid="{69AC9F7A-5398-410B-84D7-6E4E83EE57E8}" name="Buying Price" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{7A69A202-D8EA-41A6-95D3-0015094D703C}" name="Selling Price" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{9741974B-D6ED-460F-9C8D-702EA0D3DA7D}" name="Total Buying" dataDxfId="7" dataCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{985209AE-C175-4412-A5E0-92E6C0F7A6EF}" name="Total Sales" dataDxfId="6" dataCellStyle="Currency"/>
+    <tableColumn id="11" xr3:uid="{D7D84B77-8B5F-41B1-AB70-CCD67DBF458A}" name="Profit" dataDxfId="5">
       <calculatedColumnFormula>J2-I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{0240461C-84D0-4D86-932C-AF423A8D38ED}" name="States" dataDxfId="5" dataCellStyle="Currency"/>
-    <tableColumn id="16" xr3:uid="{C56BEBA8-7E65-47FD-9D79-775F179056CE}" name="City" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{FDAE72C0-FF85-48BA-B205-D8FA1647ABCC}" name="Month" dataDxfId="3">
+    <tableColumn id="15" xr3:uid="{0240461C-84D0-4D86-932C-AF423A8D38ED}" name="States" dataDxfId="4" dataCellStyle="Currency"/>
+    <tableColumn id="16" xr3:uid="{C56BEBA8-7E65-47FD-9D79-775F179056CE}" name="City" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{FDAE72C0-FF85-48BA-B205-D8FA1647ABCC}" name="Month" dataDxfId="2">
       <calculatedColumnFormula>TEXT(Table1[[#This Row],[Date]],"mmm")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -30204,118 +30190,118 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="str">
+      <c r="A1" s="49" t="str">
         <f>IF(ISEVEN('07.DRW'!K4),"Total Sales","Total Profit")</f>
         <v>Total Profit</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="45"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="51"/>
     </row>
     <row r="2" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="55"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="54"/>
     </row>
     <row r="3" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="53"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="54"/>
-      <c r="R3" s="55"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="54"/>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="R4" s="48"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="57"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="49" t="s">
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="41" t="s">
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="47" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="41"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
@@ -30364,10 +30350,10 @@
       <c r="Q6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="R6" s="41"/>
+      <c r="R6" s="47"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="43" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="39">
@@ -30434,13 +30420,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A7, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>21100.380000000019</v>
       </c>
-      <c r="R7" s="59">
+      <c r="R7" s="44">
         <f t="shared" ref="R7:R17" si="0">SUM(B7:Q7)</f>
         <v>429926.09999999992</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="43" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="39">
@@ -30507,13 +30493,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A8, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>17868.879999999997</v>
       </c>
-      <c r="R8" s="59">
+      <c r="R8" s="44">
         <f t="shared" si="0"/>
         <v>764890.87</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="43" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="39">
@@ -30580,13 +30566,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A9, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>19574.729999999981</v>
       </c>
-      <c r="R9" s="59">
+      <c r="R9" s="44">
         <f t="shared" si="0"/>
         <v>623162.27999999991</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="43" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="39">
@@ -30653,13 +30639,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A10, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>79311.17</v>
       </c>
-      <c r="R10" s="59">
+      <c r="R10" s="44">
         <f t="shared" si="0"/>
         <v>256481.87000000005</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="43" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="39">
@@ -30726,13 +30712,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A11, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>40377.600000000006</v>
       </c>
-      <c r="R11" s="59">
+      <c r="R11" s="44">
         <f t="shared" si="0"/>
         <v>528272.74</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="43" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="39">
@@ -30799,13 +30785,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A12, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>43898.560000000012</v>
       </c>
-      <c r="R12" s="59">
+      <c r="R12" s="44">
         <f t="shared" si="0"/>
         <v>118788.12000000002</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="43" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="39">
@@ -30872,13 +30858,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A13, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>20838.36</v>
       </c>
-      <c r="R13" s="59">
+      <c r="R13" s="44">
         <f t="shared" si="0"/>
         <v>691495.34000000008</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="43" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="39">
@@ -30945,13 +30931,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A14, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>11021.760000000002</v>
       </c>
-      <c r="R14" s="59">
+      <c r="R14" s="44">
         <f t="shared" si="0"/>
         <v>737620.37000000011</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="43" t="s">
         <v>31</v>
       </c>
       <c r="B15" s="39">
@@ -31018,13 +31004,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A15, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>0</v>
       </c>
-      <c r="R15" s="59">
+      <c r="R15" s="44">
         <f t="shared" si="0"/>
         <v>484614.46</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="43" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="39">
@@ -31091,13 +31077,13 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A16, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>58108.809999999969</v>
       </c>
-      <c r="R16" s="59">
+      <c r="R16" s="44">
         <f t="shared" si="0"/>
         <v>603148.91999999993</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
       <c r="B17" s="39">
@@ -31164,7 +31150,7 @@
         <f>SUMIFS(IF(ISEVEN('07.DRW'!$K$4),INDEX(Table1[],,10),INDEX(Table1[],,11)), Table1[[Customer name]:[Customer name]], '02.MIS Report Table'!$A17, Table1[[Payment Method]:[Payment Method]], "Cash", Table1[[Product]:[Product]], '02.MIS Report Table'!I$6)</f>
         <v>19723.200000000012</v>
       </c>
-      <c r="R17" s="59">
+      <c r="R17" s="44">
         <f t="shared" si="0"/>
         <v>364922.49000000011</v>
       </c>
@@ -31173,77 +31159,74 @@
       <c r="A18" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="59">
-        <f>SUM(B7:B17)</f>
+      <c r="B18" s="44">
+        <f t="shared" ref="B18:Q18" si="1">SUM(B7:B17)</f>
         <v>408777.19999999995</v>
       </c>
-      <c r="C18" s="59">
-        <f>SUM(C7:C17)</f>
+      <c r="C18" s="44">
+        <f t="shared" si="1"/>
         <v>574591.1100000001</v>
       </c>
-      <c r="D18" s="59">
-        <f>SUM(D7:D17)</f>
+      <c r="D18" s="44">
+        <f t="shared" si="1"/>
         <v>525382.25</v>
       </c>
-      <c r="E18" s="59">
-        <f>SUM(E7:E17)</f>
+      <c r="E18" s="44">
+        <f t="shared" si="1"/>
         <v>304217.32000000007</v>
       </c>
-      <c r="F18" s="59">
-        <f>SUM(F7:F17)</f>
+      <c r="F18" s="44">
+        <f t="shared" si="1"/>
         <v>138896.40000000011</v>
       </c>
-      <c r="G18" s="59">
-        <f>SUM(G7:G17)</f>
+      <c r="G18" s="44">
+        <f t="shared" si="1"/>
         <v>348399.24</v>
       </c>
-      <c r="H18" s="59">
-        <f>SUM(H7:H17)</f>
+      <c r="H18" s="44">
+        <f t="shared" si="1"/>
         <v>327336.28000000009</v>
       </c>
-      <c r="I18" s="59">
-        <f>SUM(I7:I17)</f>
+      <c r="I18" s="44">
+        <f t="shared" si="1"/>
         <v>327682.08000000007</v>
       </c>
-      <c r="J18" s="59">
-        <f>SUM(J7:J17)</f>
+      <c r="J18" s="44">
+        <f t="shared" si="1"/>
         <v>353979.65000000008</v>
       </c>
-      <c r="K18" s="59">
-        <f>SUM(K7:K17)</f>
+      <c r="K18" s="44">
+        <f t="shared" si="1"/>
         <v>322670.25000000006</v>
       </c>
-      <c r="L18" s="59">
-        <f>SUM(L7:L17)</f>
+      <c r="L18" s="44">
+        <f t="shared" si="1"/>
         <v>197934.30000000005</v>
       </c>
-      <c r="M18" s="59">
-        <f>SUM(M7:M17)</f>
+      <c r="M18" s="44">
+        <f t="shared" si="1"/>
         <v>260293.16999999998</v>
       </c>
-      <c r="N18" s="59">
-        <f>SUM(N7:N17)</f>
+      <c r="N18" s="44">
+        <f t="shared" si="1"/>
         <v>450743.17000000004</v>
       </c>
-      <c r="O18" s="59">
-        <f>SUM(O7:O17)</f>
+      <c r="O18" s="44">
+        <f t="shared" si="1"/>
         <v>393164.2</v>
       </c>
-      <c r="P18" s="59">
-        <f>SUM(P7:P17)</f>
+      <c r="P18" s="44">
+        <f t="shared" si="1"/>
         <v>337433.49</v>
       </c>
-      <c r="Q18" s="59">
-        <f>SUM(Q7:Q17)</f>
+      <c r="Q18" s="44">
+        <f t="shared" si="1"/>
         <v>331823.45</v>
       </c>
-      <c r="R18" s="60">
-        <f t="shared" ref="J18:R18" si="1">SUM(R7:R17)</f>
+      <c r="R18" s="45">
+        <f t="shared" ref="R18" si="2">SUM(R7:R17)</f>
         <v>5603323.5600000005</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="E20" s="52"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="E24" s="2"/>
@@ -31260,10 +31243,10 @@
     <mergeCell ref="A1:R4"/>
   </mergeCells>
   <conditionalFormatting sqref="B7:R18">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31319,20 +31302,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="58" t="s">
         <v>399</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -31653,20 +31636,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="58" t="s">
         <v>398</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
     </row>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -32065,20 +32048,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="58" t="s">
         <v>400</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -32774,26 +32757,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="49" t="s">
         <v>396</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="45"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="51"/>
     </row>
     <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="46"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="48"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="57"/>
       <c r="N2" t="s">
         <v>393</v>
       </c>
@@ -32808,7 +32791,7 @@
       <c r="C3" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="56" t="s">
+      <c r="K3" s="41" t="s">
         <v>397</v>
       </c>
     </row>
@@ -32822,7 +32805,7 @@
       <c r="C4" s="2">
         <v>2890845</v>
       </c>
-      <c r="K4" s="57">
+      <c r="K4" s="42">
         <v>14963</v>
       </c>
       <c r="N4" t="s">
